--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringr_median_a_2018_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringr_median_a_2018_atacama.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:45</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -828,10 +828,10 @@
         <v>0.36</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="15">
@@ -851,7 +851,7 @@
         <v>-0.04</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.55</v>
@@ -874,7 +874,7 @@
         <v>0.41</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.18</v>
@@ -888,7 +888,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>9</v>
@@ -897,10 +897,10 @@
         <v>0.32</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringr_median_a_2018_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringr_median_a_2018_atacama.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:35</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringr_median_a_2018_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringr_median_a_2018_atacama.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
